--- a/diseases/d008/2000-2004.xlsx
+++ b/diseases/d008/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33703,7 +33703,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34478,7 +34478,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37578,7 +37578,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40134,7 +40134,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -44784,7 +44784,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -47109,7 +47109,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">

--- a/diseases/d008/2000-2004.xlsx
+++ b/diseases/d008/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33703,7 +33703,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34478,7 +34478,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37578,7 +37578,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40134,7 +40134,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -44784,7 +44784,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -47109,7 +47109,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">

--- a/diseases/d008/2000-2004.xlsx
+++ b/diseases/d008/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21082,7 +21082,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24182,7 +24182,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27282,7 +27282,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -30613,7 +30613,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31388,7 +31388,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32163,7 +32163,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33713,7 +33713,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34488,7 +34488,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36038,7 +36038,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37588,7 +37588,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38363,7 +38363,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40144,7 +40144,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40919,7 +40919,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -41694,7 +41694,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -42469,7 +42469,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -44019,7 +44019,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -44794,7 +44794,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -46344,7 +46344,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -47119,7 +47119,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN244" t="b">

--- a/diseases/d008/2000-2004.xlsx
+++ b/diseases/d008/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33703,7 +33703,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34478,7 +34478,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37578,7 +37578,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40134,7 +40134,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -44784,7 +44784,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -47109,7 +47109,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">

--- a/diseases/d008/2000-2004.xlsx
+++ b/diseases/d008/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33703,7 +33703,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34478,7 +34478,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37578,7 +37578,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40134,7 +40134,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -44784,7 +44784,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -47109,7 +47109,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">

--- a/diseases/d008/2000-2004.xlsx
+++ b/diseases/d008/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31378,7 +31378,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33703,7 +33703,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34478,7 +34478,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35253,7 +35253,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37578,7 +37578,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40134,7 +40134,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -44784,7 +44784,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -47109,7 +47109,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
